--- a/data/trans_orig/P11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P11-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2007</t>
+          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>29672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23493</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47899</t>
+          <t>48359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>40785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69502</t>
+          <t>69590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>37732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68533</t>
+          <t>66150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68408</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105147</t>
+          <t>103837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114190</t>
+          <t>113557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160509</t>
+          <t>159583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76115</t>
+          <t>74350</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109363</t>
+          <t>110250</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152903</t>
+          <t>151078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>202987</t>
+          <t>199651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>235361</t>
+          <t>240680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>302110</t>
+          <t>298730</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>157723</t>
+          <t>160299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>203512</t>
+          <t>208191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>291512</t>
+          <t>289918</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>350804</t>
+          <t>353741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>463646</t>
+          <t>463473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>542875</t>
+          <t>540512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>656983</t>
+          <t>655023</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>718580</t>
+          <t>714600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>664883</t>
+          <t>663675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>732194</t>
+          <t>738339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1336334</t>
+          <t>1336189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1430107</t>
+          <t>1432954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31899</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34272</t>
+          <t>33633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40946</t>
+          <t>41678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40239</t>
+          <t>40630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69099</t>
+          <t>68456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>53828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45288</t>
+          <t>46132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77115</t>
+          <t>76045</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81041</t>
+          <t>80902</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119975</t>
+          <t>120212</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104003</t>
+          <t>106271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149180</t>
+          <t>148100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160513</t>
+          <t>162131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216155</t>
+          <t>213646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279626</t>
+          <t>276795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>344136</t>
+          <t>343340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1470710</t>
+          <t>1472902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1526840</t>
+          <t>1523335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1261097</t>
+          <t>1264058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1326777</t>
+          <t>1324312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2755993</t>
+          <t>2754934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2835326</t>
+          <t>2836898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15829</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28838</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>31926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42781</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23395</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46298</t>
+          <t>47623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34947</t>
+          <t>35237</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60909</t>
+          <t>62327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64392</t>
+          <t>64433</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100457</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>477635</t>
+          <t>479607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>508381</t>
+          <t>509328</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>378064</t>
+          <t>378327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>411904</t>
+          <t>411258</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>867541</t>
+          <t>866611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>913250</t>
+          <t>913135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>42271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>38818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70991</t>
+          <t>69240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65656</t>
+          <t>66961</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101012</t>
+          <t>102020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67249</t>
+          <t>69919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104364</t>
+          <t>105626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103080</t>
+          <t>102685</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147165</t>
+          <t>145501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>181146</t>
+          <t>181541</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233994</t>
+          <t>236082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>120486</t>
+          <t>118111</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>163093</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>227339</t>
+          <t>225766</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>289377</t>
+          <t>287453</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>360902</t>
+          <t>359883</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>438459</t>
+          <t>437766</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>308539</t>
+          <t>305354</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>378681</t>
+          <t>374715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>512552</t>
+          <t>509992</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>597428</t>
+          <t>600860</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>839515</t>
+          <t>835059</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>948038</t>
+          <t>950142</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2633678</t>
+          <t>2633467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2723560</t>
+          <t>2722206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2342857</t>
+          <t>2336818</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2447853</t>
+          <t>2445226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5000553</t>
+          <t>5006041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5141367</t>
+          <t>5144842</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2012</t>
+          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51418</t>
+          <t>50990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70176</t>
+          <t>70771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107850</t>
+          <t>106948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102725</t>
+          <t>102834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146629</t>
+          <t>148468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55916</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90815</t>
+          <t>91542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138917</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>190753</t>
+          <t>185565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>200641</t>
+          <t>204040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>260196</t>
+          <t>263636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54688</t>
+          <t>55464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90450</t>
+          <t>90489</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131663</t>
+          <t>133754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182881</t>
+          <t>184770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>201689</t>
+          <t>198393</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>260614</t>
+          <t>258852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>133242</t>
+          <t>134097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>181037</t>
+          <t>184381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>262797</t>
+          <t>263492</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324079</t>
+          <t>324568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>411753</t>
+          <t>411593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>490479</t>
+          <t>490667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>602904</t>
+          <t>601831</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>664421</t>
+          <t>664475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604843</t>
+          <t>599500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>678328</t>
+          <t>678653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1224190</t>
+          <t>1226137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1318832</t>
+          <t>1327616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38381</t>
+          <t>38750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>28813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53040</t>
+          <t>53971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>29122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55835</t>
+          <t>56956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46727</t>
+          <t>47381</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81335</t>
+          <t>82392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85506</t>
+          <t>84141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127299</t>
+          <t>127386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>29241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52506</t>
+          <t>53740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61575</t>
+          <t>62185</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98611</t>
+          <t>98508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96367</t>
+          <t>98354</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141280</t>
+          <t>141341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134484</t>
+          <t>137512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190514</t>
+          <t>185441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166956</t>
+          <t>170158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>223116</t>
+          <t>221979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>319467</t>
+          <t>322885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>393468</t>
+          <t>396062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1666993</t>
+          <t>1667863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1731863</t>
+          <t>1729022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1356372</t>
+          <t>1355574</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1424357</t>
+          <t>1426544</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3045008</t>
+          <t>3041501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3139409</t>
+          <t>3134427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,82 +5184,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11913</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6008</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>21521</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>19000</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>11528</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>33381</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>3,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11913</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5955</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>21286</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>19000</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>10508</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>31944</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>32186</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44786</t>
+          <t>44899</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42350</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45316</t>
+          <t>44971</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78830</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>410711</t>
+          <t>410648</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>442015</t>
+          <t>440764</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>392550</t>
+          <t>392110</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>420602</t>
+          <t>419913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>811990</t>
+          <t>810570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>854001</t>
+          <t>855096</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39186</t>
+          <t>39715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70893</t>
+          <t>69729</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95064</t>
+          <t>92108</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136859</t>
+          <t>133486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139947</t>
+          <t>143066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>193046</t>
+          <t>191551</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98979</t>
+          <t>99126</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>143988</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205796</t>
+          <t>204883</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>266185</t>
+          <t>267308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>316967</t>
+          <t>317491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>390883</t>
+          <t>393980</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100341</t>
+          <t>99406</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>146934</t>
+          <t>143329</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>217421</t>
+          <t>218204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>280327</t>
+          <t>278463</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>329326</t>
+          <t>331646</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>407893</t>
+          <t>403804</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>311275</t>
+          <t>313181</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>379566</t>
+          <t>386280</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>477245</t>
+          <t>476279</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>561646</t>
+          <t>564349</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>808786</t>
+          <t>812224</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>922199</t>
+          <t>921441</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2718321</t>
+          <t>2712696</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2808905</t>
+          <t>2808900</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2381687</t>
+          <t>2380400</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2496475</t>
+          <t>2498058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5127306</t>
+          <t>5126375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5278734</t>
+          <t>5268863</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2016</t>
+          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35989</t>
+          <t>35675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56715</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91911</t>
+          <t>91716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78187</t>
+          <t>79102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120127</t>
+          <t>117169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35770</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61183</t>
+          <t>61924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97994</t>
+          <t>100049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143295</t>
+          <t>143851</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141163</t>
+          <t>142952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>191863</t>
+          <t>193125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48852</t>
+          <t>48477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78690</t>
+          <t>77886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96788</t>
+          <t>97739</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143685</t>
+          <t>140789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155980</t>
+          <t>156479</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>207968</t>
+          <t>208086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103320</t>
+          <t>101167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143137</t>
+          <t>140266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>185155</t>
+          <t>187042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>238080</t>
+          <t>237823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301979</t>
+          <t>300056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>371213</t>
+          <t>365114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469965</t>
+          <t>467625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>519029</t>
+          <t>519843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429914</t>
+          <t>426027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492869</t>
+          <t>491053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912891</t>
+          <t>914056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>998182</t>
+          <t>997636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,47 +7348,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>29868</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19934</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41934</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>29868</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19382</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>43093</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37267</t>
+          <t>37291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67405</t>
+          <t>68387</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27258</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54241</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>59787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96938</t>
+          <t>95909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94081</t>
+          <t>92643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137447</t>
+          <t>139226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45356</t>
+          <t>46276</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77291</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55545</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93091</t>
+          <t>89792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112190</t>
+          <t>110649</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>159421</t>
+          <t>158118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172938</t>
+          <t>170073</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>226336</t>
+          <t>227329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195583</t>
+          <t>199646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259788</t>
+          <t>256343</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387972</t>
+          <t>387774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467631</t>
+          <t>467163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1709841</t>
+          <t>1709265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1776131</t>
+          <t>1777520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1535334</t>
+          <t>1534771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1615232</t>
+          <t>1608599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3264710</t>
+          <t>3260392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3363529</t>
+          <t>3362718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>36620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19657</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42786</t>
+          <t>43398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65473</t>
+          <t>65945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63398</t>
+          <t>65028</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100605</t>
+          <t>101871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>472210</t>
+          <t>472727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>502369</t>
+          <t>502294</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>441856</t>
+          <t>441940</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>477062</t>
+          <t>478339</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,47 +8517,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>948855</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>924139</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>971122</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>87,17%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>948855</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>923541</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>972057</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33192</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61010</t>
+          <t>60961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89766</t>
+          <t>86573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132164</t>
+          <t>130655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128300</t>
+          <t>128429</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>181942</t>
+          <t>179902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76119</t>
+          <t>76128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116023</t>
+          <t>116319</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>184448</t>
+          <t>188262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244898</t>
+          <t>243737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>274214</t>
+          <t>272039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>341931</t>
+          <t>343559</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>113724</t>
+          <t>116602</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>159466</t>
+          <t>161653</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>178626</t>
+          <t>178268</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>235291</t>
+          <t>233964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>305299</t>
+          <t>310676</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>378184</t>
+          <t>383933</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>312890</t>
+          <t>314827</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>385117</t>
+          <t>387342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>442254</t>
+          <t>448220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>530135</t>
+          <t>532527</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>781145</t>
+          <t>784782</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>894231</t>
+          <t>897816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2681602</t>
+          <t>2681633</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2776992</t>
+          <t>2773295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2439426</t>
+          <t>2443421</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2548214</t>
+          <t>2550807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5153936</t>
+          <t>5149169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5294012</t>
+          <t>5288558</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2023</t>
+          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>23820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>44362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69544</t>
+          <t>68381</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93811</t>
+          <t>92959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97749</t>
+          <t>99004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>130334</t>
+          <t>129198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>55727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81843</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121735</t>
+          <t>121726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>155593</t>
+          <t>158742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185262</t>
+          <t>184046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229693</t>
+          <t>228525</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47381</t>
+          <t>47439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72923</t>
+          <t>72243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100788</t>
+          <t>99415</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>130225</t>
+          <t>129814</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>154288</t>
+          <t>154395</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>193282</t>
+          <t>192878</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55486</t>
+          <t>56195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82813</t>
+          <t>81910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134379</t>
+          <t>135777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167431</t>
+          <t>167052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198631</t>
+          <t>196337</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>240001</t>
+          <t>238488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266541</t>
+          <t>264272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>308003</t>
+          <t>307766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248744</t>
+          <t>246930</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289534</t>
+          <t>291459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>523928</t>
+          <t>527619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>584967</t>
+          <t>587847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>23561</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52107</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69694</t>
+          <t>68114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70210</t>
+          <t>71132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110734</t>
+          <t>112319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67120</t>
+          <t>67576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117976</t>
+          <t>120815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83170</t>
+          <t>85401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139354</t>
+          <t>136524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164800</t>
+          <t>163529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243252</t>
+          <t>244438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86223</t>
+          <t>86206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151019</t>
+          <t>152416</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118203</t>
+          <t>120820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190878</t>
+          <t>193266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>228913</t>
+          <t>230884</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329873</t>
+          <t>333446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178846</t>
+          <t>176516</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>300248</t>
+          <t>299593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>294610</t>
+          <t>294462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>993036</t>
+          <t>958748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>534937</t>
+          <t>541996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1277374</t>
+          <t>1306448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1700908</t>
+          <t>1699246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1920376</t>
+          <t>1928318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1026024</t>
+          <t>1042220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1592476</t>
+          <t>1592364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2740462</t>
+          <t>2702743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3409246</t>
+          <t>3388726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>36195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>35091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57153</t>
+          <t>58667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39218</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53092</t>
+          <t>53185</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56107</t>
+          <t>56268</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85612</t>
+          <t>85043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53574</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85458</t>
+          <t>85791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76724</t>
+          <t>76678</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107041</t>
+          <t>108065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139081</t>
+          <t>135565</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>185670</t>
+          <t>182180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>503262</t>
+          <t>501844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>542016</t>
+          <t>542892</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>469242</t>
+          <t>466228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>506622</t>
+          <t>507173</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>981832</t>
+          <t>985465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1037712</t>
+          <t>1041049</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59260</t>
+          <t>57743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>96029</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118082</t>
+          <t>118339</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163575</t>
+          <t>164428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193317</t>
+          <t>190112</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>254072</t>
+          <t>253100</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>143566</t>
+          <t>142541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>212393</t>
+          <t>210156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230142</t>
+          <t>227547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>310350</t>
+          <t>311488</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>400195</t>
+          <t>392739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>508664</t>
+          <t>509877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167552</t>
+          <t>163570</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>244931</t>
+          <t>240639</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>261965</t>
+          <t>262732</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>355228</t>
+          <t>354946</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>463462</t>
+          <t>463395</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>582950</t>
+          <t>582480</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>304241</t>
+          <t>307662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>440805</t>
+          <t>437149</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>538979</t>
+          <t>538188</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1287612</t>
+          <t>1263404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>905667</t>
+          <t>914864</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1649704</t>
+          <t>1803468</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2497929</t>
+          <t>2507663</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2775639</t>
+          <t>2774641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1738150</t>
+          <t>1786580</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2339365</t>
+          <t>2341335</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4339285</t>
+          <t>4228183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5013952</t>
+          <t>5000061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P11-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>30107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23780</t>
+          <t>24204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48359</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>40345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69590</t>
+          <t>69045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37732</t>
+          <t>38908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66150</t>
+          <t>66410</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68408</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103837</t>
+          <t>104245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113557</t>
+          <t>114520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159583</t>
+          <t>162036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74350</t>
+          <t>76730</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>113145</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>151078</t>
+          <t>152024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>199651</t>
+          <t>201934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240680</t>
+          <t>239373</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>298730</t>
+          <t>299795</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208191</t>
+          <t>206125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289918</t>
+          <t>290654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>353741</t>
+          <t>352181</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>463473</t>
+          <t>463690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>540512</t>
+          <t>542414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655023</t>
+          <t>654986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>714600</t>
+          <t>716254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>663675</t>
+          <t>663225</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>738339</t>
+          <t>735322</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1336189</t>
+          <t>1337869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1432954</t>
+          <t>1433297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,07%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32915</t>
+          <t>32079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33633</t>
+          <t>34780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41678</t>
+          <t>40932</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40630</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68456</t>
+          <t>69824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29205</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53828</t>
+          <t>54000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46132</t>
+          <t>45319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76045</t>
+          <t>76624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80902</t>
+          <t>82846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120212</t>
+          <t>122949</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106271</t>
+          <t>105170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148100</t>
+          <t>149147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162131</t>
+          <t>161193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213646</t>
+          <t>213656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276795</t>
+          <t>280526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>343340</t>
+          <t>350414</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1472902</t>
+          <t>1473655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1523335</t>
+          <t>1524935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1264058</t>
+          <t>1264517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1324312</t>
+          <t>1328214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2754934</t>
+          <t>2749876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2836898</t>
+          <t>2834659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>16016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>27947</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>33702</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43074</t>
+          <t>41958</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47623</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62327</t>
+          <t>61618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64433</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100865</t>
+          <t>100833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>479607</t>
+          <t>478271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>509328</t>
+          <t>508138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>378327</t>
+          <t>378566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>411258</t>
+          <t>412453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>866611</t>
+          <t>864547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>913135</t>
+          <t>911274</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,66%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38818</t>
+          <t>40053</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69240</t>
+          <t>70830</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66961</t>
+          <t>67439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102020</t>
+          <t>103400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69919</t>
+          <t>70225</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105626</t>
+          <t>106696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102685</t>
+          <t>101151</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145501</t>
+          <t>145393</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>181541</t>
+          <t>179600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>236082</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118111</t>
+          <t>120007</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>163093</t>
+          <t>165108</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>225766</t>
+          <t>228142</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>289526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>359883</t>
+          <t>358742</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>437766</t>
+          <t>437965</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>305354</t>
+          <t>308123</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>374715</t>
+          <t>376279</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>509992</t>
+          <t>509796</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>600860</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>835059</t>
+          <t>840600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>950142</t>
+          <t>953077</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2633467</t>
+          <t>2636569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2722206</t>
+          <t>2723299</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2336818</t>
+          <t>2334513</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2445226</t>
+          <t>2440383</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5006041</t>
+          <t>5006945</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5144842</t>
+          <t>5147285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26443</t>
+          <t>25751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50990</t>
+          <t>51161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70771</t>
+          <t>70278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106948</t>
+          <t>105924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102834</t>
+          <t>104451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148468</t>
+          <t>149279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>55487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91542</t>
+          <t>91630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138758</t>
+          <t>136268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185565</t>
+          <t>185155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204040</t>
+          <t>204528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263636</t>
+          <t>260317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55464</t>
+          <t>54386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90489</t>
+          <t>87887</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133754</t>
+          <t>134427</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>184770</t>
+          <t>181260</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>198393</t>
+          <t>202804</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>258852</t>
+          <t>258346</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134097</t>
+          <t>133881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184381</t>
+          <t>182040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>263492</t>
+          <t>263405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324568</t>
+          <t>322684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>411593</t>
+          <t>411436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>490667</t>
+          <t>487714</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>601831</t>
+          <t>605366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>664475</t>
+          <t>666671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>599500</t>
+          <t>603031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>678653</t>
+          <t>677225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1226137</t>
+          <t>1227745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1327616</t>
+          <t>1324549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,4%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38750</t>
+          <t>39124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53971</t>
+          <t>54265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>29643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56956</t>
+          <t>57771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47381</t>
+          <t>47177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82392</t>
+          <t>81707</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84141</t>
+          <t>85287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127386</t>
+          <t>128160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29241</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53740</t>
+          <t>53845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62185</t>
+          <t>63382</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98508</t>
+          <t>98617</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98354</t>
+          <t>98487</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141341</t>
+          <t>141707</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137512</t>
+          <t>137159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185441</t>
+          <t>189467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>170158</t>
+          <t>170627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>221979</t>
+          <t>227065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322885</t>
+          <t>314927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>396062</t>
+          <t>391714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1667863</t>
+          <t>1668305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1729022</t>
+          <t>1731375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1355574</t>
+          <t>1355377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1426544</t>
+          <t>1424185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3041501</t>
+          <t>3043933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3134427</t>
+          <t>3136473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33381</t>
+          <t>31133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32186</t>
+          <t>31709</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20623</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44899</t>
+          <t>47133</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,49 +5410,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>29496</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>19530</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>42956</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>9,37%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>29496</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>20501</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>42346</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>52</t>
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>44257</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>76161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>410648</t>
+          <t>411170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>440764</t>
+          <t>441290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>392110</t>
+          <t>390471</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>419913</t>
+          <t>420162</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>810570</t>
+          <t>816844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>855096</t>
+          <t>857872</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>40038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69729</t>
+          <t>71457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92108</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133486</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>143066</t>
+          <t>140638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>191551</t>
+          <t>192287</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99126</t>
+          <t>99694</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>143988</t>
+          <t>147991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204883</t>
+          <t>205064</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267308</t>
+          <t>268893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>317491</t>
+          <t>321429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>393980</t>
+          <t>395116</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99406</t>
+          <t>98694</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143329</t>
+          <t>143534</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>218204</t>
+          <t>219767</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>278463</t>
+          <t>279133</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>331646</t>
+          <t>327088</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>403804</t>
+          <t>405139</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>313181</t>
+          <t>313146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>386280</t>
+          <t>384679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>476279</t>
+          <t>475990</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>564349</t>
+          <t>562785</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>812224</t>
+          <t>810464</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>921441</t>
+          <t>925680</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2712696</t>
+          <t>2705542</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2808900</t>
+          <t>2806826</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2380400</t>
+          <t>2384263</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2498058</t>
+          <t>2501471</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5126375</t>
+          <t>5130964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5268863</t>
+          <t>5273017</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>15319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35675</t>
+          <t>36671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56147</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91716</t>
+          <t>90667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>78551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117169</t>
+          <t>119878</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>35956</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61924</t>
+          <t>60831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100049</t>
+          <t>96962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143851</t>
+          <t>142965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142952</t>
+          <t>143676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>193125</t>
+          <t>194782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48477</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77886</t>
+          <t>79240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97739</t>
+          <t>98468</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140789</t>
+          <t>143906</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>156479</t>
+          <t>156400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>208086</t>
+          <t>210095</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101167</t>
+          <t>100522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>140266</t>
+          <t>141088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187042</t>
+          <t>187790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237823</t>
+          <t>237725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300056</t>
+          <t>298650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>365114</t>
+          <t>368067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467625</t>
+          <t>471502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>519843</t>
+          <t>521792</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426027</t>
+          <t>427742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491053</t>
+          <t>492772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914056</t>
+          <t>911008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>997636</t>
+          <t>998333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>30957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>20151</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41934</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37291</t>
+          <t>36658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68387</t>
+          <t>67319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>26217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>52482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59787</t>
+          <t>61839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95909</t>
+          <t>96629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92643</t>
+          <t>95418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139226</t>
+          <t>139808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>46865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77978</t>
+          <t>79870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56367</t>
+          <t>55477</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89792</t>
+          <t>92002</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110649</t>
+          <t>111741</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158118</t>
+          <t>158772</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170073</t>
+          <t>171695</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227329</t>
+          <t>228603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>199646</t>
+          <t>200117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256343</t>
+          <t>259881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387774</t>
+          <t>383224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467163</t>
+          <t>464492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1709265</t>
+          <t>1707181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1777520</t>
+          <t>1777741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1534771</t>
+          <t>1534199</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1608599</t>
+          <t>1608159</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3260392</t>
+          <t>3265917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3362718</t>
+          <t>3369570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>27960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36620</t>
+          <t>36733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>24650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>24405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40910</t>
+          <t>41371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43398</t>
+          <t>42870</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>37906</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65945</t>
+          <t>66740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65028</t>
+          <t>63137</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101871</t>
+          <t>100040</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>471847</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>502294</t>
+          <t>502156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>441940</t>
+          <t>441370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>478339</t>
+          <t>477104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924139</t>
+          <t>921255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>971122</t>
+          <t>970812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33675</t>
+          <t>32861</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60961</t>
+          <t>60493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86573</t>
+          <t>88220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130655</t>
+          <t>130920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128429</t>
+          <t>128921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179902</t>
+          <t>180603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76128</t>
+          <t>76618</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116319</t>
+          <t>115189</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188262</t>
+          <t>186663</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>243737</t>
+          <t>248721</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272039</t>
+          <t>276827</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>343559</t>
+          <t>343251</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>116602</t>
+          <t>114522</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161653</t>
+          <t>160457</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>178268</t>
+          <t>175860</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>233964</t>
+          <t>234374</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>310676</t>
+          <t>302895</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>383933</t>
+          <t>382700</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>314827</t>
+          <t>312612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>387342</t>
+          <t>387463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>448220</t>
+          <t>446578</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>532527</t>
+          <t>532884</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>784782</t>
+          <t>778840</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>897816</t>
+          <t>892879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2681633</t>
+          <t>2681111</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2773295</t>
+          <t>2776059</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2443421</t>
+          <t>2438107</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2550807</t>
+          <t>2550886</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5149169</t>
+          <t>5153719</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5288558</t>
+          <t>5304710</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32671</t>
+          <t>34252</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44362</t>
+          <t>46183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>80169</t>
+          <t>87140</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68381</t>
+          <t>74238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92959</t>
+          <t>100740</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>112840</t>
+          <t>121392</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99004</t>
+          <t>105450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129198</t>
+          <t>139341</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68199</t>
+          <t>71997</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55727</t>
+          <t>57736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82409</t>
+          <t>86754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>137597</t>
+          <t>145359</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121726</t>
+          <t>128744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158742</t>
+          <t>161165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>205796</t>
+          <t>217357</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184046</t>
+          <t>195685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228525</t>
+          <t>239666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58700</t>
+          <t>64103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47439</t>
+          <t>50935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72243</t>
+          <t>78756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>114767</t>
+          <t>124224</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>99415</t>
+          <t>108655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129814</t>
+          <t>141341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>173467</t>
+          <t>188328</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>154395</t>
+          <t>169475</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>192878</t>
+          <t>209358</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67620</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56195</t>
+          <t>63456</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81910</t>
+          <t>95048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>151308</t>
+          <t>162552</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135777</t>
+          <t>145523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167052</t>
+          <t>181364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>218929</t>
+          <t>240171</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196337</t>
+          <t>218750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238488</t>
+          <t>263622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>287748</t>
+          <t>330557</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264272</t>
+          <t>308215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307766</t>
+          <t>351664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>269493</t>
+          <t>300360</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246930</t>
+          <t>276929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291459</t>
+          <t>322161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>557241</t>
+          <t>630917</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>527619</t>
+          <t>600957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>587847</t>
+          <t>664055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819635</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1268273</t>
+          <t>1398165</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1268273</t>
+          <t>1398165</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1268273</t>
+          <t>1398165</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37146</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23561</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50406</t>
+          <t>54535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53773</t>
+          <t>61185</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38069</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68114</t>
+          <t>75093</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>90919</t>
+          <t>101671</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>84197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112319</t>
+          <t>118927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95784</t>
+          <t>101528</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>83451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120815</t>
+          <t>123165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>112845</t>
+          <t>126092</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85401</t>
+          <t>107826</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136524</t>
+          <t>147756</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>208629</t>
+          <t>227620</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163529</t>
+          <t>201450</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244438</t>
+          <t>257285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>123705</t>
+          <t>134678</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>114452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>152416</t>
+          <t>160553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161978</t>
+          <t>174475</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120820</t>
+          <t>153577</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>193266</t>
+          <t>199798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>285682</t>
+          <t>309153</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>230884</t>
+          <t>278889</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>333446</t>
+          <t>343075</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>253811</t>
+          <t>275224</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176516</t>
+          <t>244819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>299593</t>
+          <t>308703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>484480</t>
+          <t>307860</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>294462</t>
+          <t>281563</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958748</t>
+          <t>336355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>738291</t>
+          <t>583083</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>541996</t>
+          <t>544876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1306448</t>
+          <t>629426</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1778234</t>
+          <t>1676608</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1699246</t>
+          <t>1631829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1928318</t>
+          <t>1720162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1424314</t>
+          <t>1501314</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1042220</t>
+          <t>1461205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1592364</t>
+          <t>1537870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3202549</t>
+          <t>3177922</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2702743</t>
+          <t>3109217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3388726</t>
+          <t>3232972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288680</t>
+          <t>2228523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288680</t>
+          <t>2228523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288680</t>
+          <t>2228523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2237390</t>
+          <t>2170926</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2237390</t>
+          <t>2170926</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2237390</t>
+          <t>2170926</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4526070</t>
+          <t>4399449</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4526070</t>
+          <t>4399449</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4526070</t>
+          <t>4399449</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>21850</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>31513</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>41872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>53363</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35091</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58667</t>
+          <t>68464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>27677</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41986</t>
+          <t>47784</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53185</t>
+          <t>59663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>69224</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56268</t>
+          <t>61736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85043</t>
+          <t>91847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68050</t>
+          <t>74791</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53310</t>
+          <t>57054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85791</t>
+          <t>94712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91352</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76678</t>
+          <t>84936</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108065</t>
+          <t>117050</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>159403</t>
+          <t>174822</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135565</t>
+          <t>153010</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182180</t>
+          <t>200359</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>523616</t>
+          <t>577171</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>501844</t>
+          <t>555321</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>542892</t>
+          <t>598275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>488770</t>
+          <t>541064</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>466228</t>
+          <t>519809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>507173</t>
+          <t>561885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1012386</t>
+          <t>1118235</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>985465</t>
+          <t>1086297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1041049</t>
+          <t>1144528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645208</t>
+          <t>710008</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645208</t>
+          <t>710008</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645208</t>
+          <t>710008</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659172</t>
+          <t>733288</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>659172</t>
+          <t>733288</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659172</t>
+          <t>733288</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1304380</t>
+          <t>1443296</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1304380</t>
+          <t>1443296</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1304380</t>
+          <t>1443296</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>83257</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57743</t>
+          <t>66675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96029</t>
+          <t>101800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>144196</t>
+          <t>161222</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118339</t>
+          <t>143143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164428</t>
+          <t>183273</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>222087</t>
+          <t>244478</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190112</t>
+          <t>220933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>253100</t>
+          <t>273154</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>182213</t>
+          <t>195376</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142541</t>
+          <t>171190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210156</t>
+          <t>225511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>277252</t>
+          <t>302964</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>227547</t>
+          <t>275677</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311488</t>
+          <t>330590</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>459465</t>
+          <t>498340</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>392739</t>
+          <t>460322</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>509877</t>
+          <t>540702</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>209643</t>
+          <t>226458</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>163570</t>
+          <t>198812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>240639</t>
+          <t>256443</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>318731</t>
+          <t>346483</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>262732</t>
+          <t>320301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>354946</t>
+          <t>380215</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>528373</t>
+          <t>572941</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>463395</t>
+          <t>534434</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>582480</t>
+          <t>617090</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>389482</t>
+          <t>427634</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>307662</t>
+          <t>388809</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>437149</t>
+          <t>468980</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>727140</t>
+          <t>570443</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>538188</t>
+          <t>535882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1263404</t>
+          <t>606917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1116623</t>
+          <t>998077</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>914864</t>
+          <t>946625</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1803468</t>
+          <t>1055894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2589597</t>
+          <t>2584336</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2507663</t>
+          <t>2528013</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2774641</t>
+          <t>2638893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2182577</t>
+          <t>2342739</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1786580</t>
+          <t>2289090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2341335</t>
+          <t>2391170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4772175</t>
+          <t>4927074</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4228183</t>
+          <t>4850406</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5000061</t>
+          <t>5001471</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3448826</t>
+          <t>3517061</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3448826</t>
+          <t>3517061</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3448826</t>
+          <t>3517061</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3723850</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3723850</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3723850</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7098723</t>
+          <t>7240910</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7098723</t>
+          <t>7240910</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7098723</t>
+          <t>7240910</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
